--- a/ig/DM_FINESS_New/ValueSet-jdv-j380-categorie-entite-geographique-exercice-rass.xlsx
+++ b/ig/DM_FINESS_New/ValueSet-jdv-j380-categorie-entite-geographique-exercice-rass.xlsx
@@ -36,7 +36,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>20251222120000</t>
+    <t>20260223120000</t>
   </si>
   <si>
     <t>Name</t>
@@ -66,7 +66,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-12-22T18:02:28.249+00:00</t>
+    <t>2026-02-23T18:02:28.249+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -84,7 +84,7 @@
     <t>Description</t>
   </si>
   <si>
-    <t>Catégories d'établissements FINESS</t>
+    <t>Ce JDV remplace le JDV-J129-CategorieEtablissement-RASS</t>
   </si>
   <si>
     <t>Purpose</t>

--- a/ig/DM_FINESS_New/ValueSet-jdv-j380-categorie-entite-geographique-exercice-rass.xlsx
+++ b/ig/DM_FINESS_New/ValueSet-jdv-j380-categorie-entite-geographique-exercice-rass.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="38" uniqueCount="35">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="41" uniqueCount="37">
   <si>
     <t>Property</t>
   </si>
@@ -109,6 +109,12 @@
   </si>
   <si>
     <t>true</t>
+  </si>
+  <si>
+    <t>niveau</t>
+  </si>
+  <si>
+    <t>4</t>
   </si>
   <si>
     <t/>
@@ -381,7 +387,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:C4"/>
+  <dimension ref="A1:C5"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="30.703125" customWidth="true"/>
@@ -415,15 +421,26 @@
         <v>32</v>
       </c>
       <c r="B3" t="s" s="2">
-        <v>32</v>
+        <v>30</v>
+      </c>
+      <c r="C3" t="s" s="2">
+        <v>33</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s" s="2">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B4" t="s" s="2">
         <v>34</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="B5" t="s" s="2">
+        <v>36</v>
       </c>
     </row>
   </sheetData>
